--- a/administrative_forms/016_workplace_injury_report_form--administrative_forms.xlsx
+++ b/administrative_forms/016_workplace_injury_report_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>employee_first_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>employee_last_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>employee_email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>injury_description</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -676,63 +676,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>witness_names</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Witness Names</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>witness_names</t>
+          <t>date_reported</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Witness Names</t>
+          <t>Date Reported</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>date_reported</t>
+          <t>time_reported</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Date Reported</t>
+          <t>Time Reported</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,23 +745,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>time_reported</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Time Reported</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Job Title</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>employee_id</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Employee ID</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>date_completed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Date Completed</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>supervisor</t>
+          <t>time_completed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Supervisor</t>
+          <t>Time Completed</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,230 +860,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>employee_id</t>
+          <t>witness</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Employee ID</t>
+          <t>Witness</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>date_completed</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Date Completed</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>time_completed</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Time Completed</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1131,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
@@ -1148,675 +941,131 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>witness_names_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>witness_names_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>witness_names_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>witness_names_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_6</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 6</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>witness_names_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_7</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 7</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>witness_names_choices</t>
+          <t>witness_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_8</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 8</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>witness_names_choices</t>
+          <t>witness_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_9</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Incomplete</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Incomplete</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Incomplete</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
